--- a/output/2026-10-06_15_Croazia_Grad_Zagreb_ATEX_Equipment-Services.xlsx
+++ b/output/2026-10-06_15_Croazia_Grad_Zagreb_ATEX_Equipment-Services.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore esclusivo in Croazia di Pepperl+Fuchs e VEGA Grieshaber KG; fornisce apparecchiature Ex certificate, isolatori galvanici, protezione da sovratensione, sistemi purge/pressurizzazione per aree pericolose ATEX. Sede: Vinkovačka ulica 24, 10110 Zagreb. Verificato tramite fetch diretto del sito ufficiale (conferma esplicita 'unico distributore autorizzato').</t>
+          <t>Distributore esclusivo in Croazia di Pepperl+Fuchs e VEGA Grieshaber KG; fornisce apparecchiature Ex certificate, isolatori galvanici, protezione da sovratensione, sistemi purge/pressurizzazione per aree pericolose ATEX. Sede: Vinkovačka ulica 24, 10110 Zagreb. Verificato tramite fetch diretto del sito ufficiale (conferma esplicita 'unico distributore autorizzato'). [DUPLICATO — vedi anche: 2026-10-05_23_Croazia_Međimurska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">

--- a/output/2026-10-06_15_Croazia_Grad_Zagreb_ATEX_Equipment-Services.xlsx
+++ b/output/2026-10-06_15_Croazia_Grad_Zagreb_ATEX_Equipment-Services.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
